--- a/data/trans_dic/P6904-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P6904-Edad-trans_dic.xlsx
@@ -527,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores musculares</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores musculares (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>34,25; 63,53</t>
+          <t>32,99; 61,54</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,93; 74,22</t>
+          <t>11,07; 74,99</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>23,74; 72,6</t>
+          <t>24,13; 73,43</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,71; 81,4</t>
+          <t>39,81; 82,18</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,59; 70,19</t>
+          <t>9,71; 69,71</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,63; 91,59</t>
+          <t>40,42; 91,62</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,47; 73,82</t>
+          <t>10,98; 75,72</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,56; 64,51</t>
+          <t>39,8; 65,04</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,23; 62,42</t>
+          <t>20,99; 64,73</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>34,64; 72,14</t>
+          <t>37,56; 73,51</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>14,64; 66,78</t>
+          <t>13,6; 66,63</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,4; 56,93</t>
+          <t>39,32; 56,53</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>45,16; 66,75</t>
+          <t>43,44; 65,78</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>46,58; 70,63</t>
+          <t>47,73; 70,25</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44,81; 77,01</t>
+          <t>44,89; 77,14</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,03; 52,82</t>
+          <t>31,0; 53,67</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,66; 59,58</t>
+          <t>34,98; 60,8</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>49,41; 75,76</t>
+          <t>48,32; 75,64</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,97; 67,02</t>
+          <t>37,51; 66,75</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>39,69; 53,09</t>
+          <t>38,6; 52,89</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>44,25; 61,19</t>
+          <t>43,35; 60,62</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>52,71; 69,22</t>
+          <t>51,79; 68,86</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,53; 68,58</t>
+          <t>46,68; 68,94</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,54; 66,97</t>
+          <t>49,11; 66,43</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>48,35; 67,87</t>
+          <t>47,64; 68,15</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>55,61; 73,7</t>
+          <t>54,39; 74,06</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>48,81; 70,12</t>
+          <t>50,38; 71,75</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,32; 68,44</t>
+          <t>45,19; 69,2</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>43,21; 67,24</t>
+          <t>44,68; 67,22</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,91; 75,15</t>
+          <t>52,53; 75,47</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>48,05; 67,23</t>
+          <t>47,08; 66,01</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>51,07; 64,77</t>
+          <t>50,5; 64,87</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49,96; 65,07</t>
+          <t>49,06; 64,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57,44; 71,15</t>
+          <t>57,5; 71,6</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>52,44; 66,37</t>
+          <t>51,76; 65,94</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,34; 57,91</t>
+          <t>37,98; 58,21</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,42; 60,72</t>
+          <t>39,05; 61,4</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>45,16; 66,2</t>
+          <t>44,3; 65,63</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53,69; 72,94</t>
+          <t>54,02; 72,29</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>49,71; 80,31</t>
+          <t>48,52; 78,78</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>30,03; 61,42</t>
+          <t>29,19; 61,64</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>50,58; 76,75</t>
+          <t>49,92; 76,71</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,3; 86,83</t>
+          <t>65,15; 87,28</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,67; 61,29</t>
+          <t>43,39; 61,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>40,3; 58,18</t>
+          <t>39,05; 58,12</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>50,02; 67,55</t>
+          <t>49,7; 67,1</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>61,97; 79,27</t>
+          <t>62,66; 80,39</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,71; 75,12</t>
+          <t>46,96; 75,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40,17; 69,91</t>
+          <t>40,89; 71,61</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>46,66; 77,51</t>
+          <t>45,13; 76,51</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,45; 73,27</t>
+          <t>50,3; 72,65</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 55,22</t>
+          <t>7,02; 54,65</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>43,4; 83,72</t>
+          <t>45,06; 84,6</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>68,43; 96,47</t>
+          <t>66,8; 96,42</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60,39; 78,5</t>
+          <t>60,59; 78,12</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>40,26; 66,98</t>
+          <t>41,59; 67,4</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>49,08; 72,75</t>
+          <t>48,57; 71,64</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>59,62; 82,19</t>
+          <t>61,51; 82,31</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>58,37; 73,02</t>
+          <t>57,58; 72,28</t>
         </is>
       </c>
     </row>
@@ -1427,12 +1427,12 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,36; 100,0</t>
+          <t>5,4; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>22,63; 100,0</t>
+          <t>32,28; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1467,12 +1467,12 @@
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>24,76; 88,22</t>
+          <t>25,51; 88,94</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
@@ -1597,7 +1597,7 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22,85; 100</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>47,36; 56,78</t>
+          <t>47,09; 56,66</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>49,21; 60,81</t>
+          <t>49,14; 60,34</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54,1; 64,93</t>
+          <t>54,09; 65,21</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55,63; 67,07</t>
+          <t>55,66; 66,98</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>45,5; 59,0</t>
+          <t>44,96; 58,31</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,37; 58,36</t>
+          <t>44,95; 58,72</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,83; 73,65</t>
+          <t>60,93; 73,49</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>59,44; 75,25</t>
+          <t>59,7; 75,66</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48,19; 55,86</t>
+          <t>48,28; 55,92</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49,01; 58,03</t>
+          <t>49,26; 58,71</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58,35; 66,58</t>
+          <t>58,47; 66,71</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>59,07; 69,2</t>
+          <t>59,13; 68,85</t>
         </is>
       </c>
     </row>
@@ -1810,7 +1810,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que su trabajo le afecta de manera que tiene dolores musculares</t>
+          <t>Población que su trabajo le afecta de manera que tiene dolores musculares (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2068,17 +2068,17 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15814; 29332</t>
+          <t>15234; 28416</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1232; 7665</t>
+          <t>1143; 7744</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4071; 12452</t>
+          <t>4138; 12594</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
@@ -2088,42 +2088,42 @@
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7886; 16165</t>
+          <t>7906; 16321</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>964; 7058</t>
+          <t>977; 7010</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4730; 10664</t>
+          <t>4706; 10667</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1606; 11326</t>
+          <t>1685; 11618</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26123; 42593</t>
+          <t>26279; 42944</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4124; 12723</t>
+          <t>4279; 13194</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>9975; 20771</t>
+          <t>10815; 21167</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>3123; 14247</t>
+          <t>2902; 14214</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>56061; 81011</t>
+          <t>55948; 80432</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>38966; 57596</t>
+          <t>37485; 56764</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>37996; 57612</t>
+          <t>38938; 57308</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26472; 45491</t>
+          <t>26516; 45569</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24599; 41873</t>
+          <t>24573; 42544</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>22898; 39363</t>
+          <t>23114; 40169</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22874; 35072</t>
+          <t>22368; 35013</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18966; 33475</t>
+          <t>18734; 33339</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>87943; 117629</t>
+          <t>85533; 117195</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>67420; 93226</t>
+          <t>66041; 92362</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>67396; 88503</t>
+          <t>66223; 88041</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50726; 74769</t>
+          <t>50896; 75158</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>62439; 84396</t>
+          <t>61898; 83718</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46877; 65808</t>
+          <t>46186; 66072</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>62913; 83369</t>
+          <t>61528; 83777</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>46632; 66988</t>
+          <t>48129; 68542</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31743; 47935</t>
+          <t>31649; 48467</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>31385; 48839</t>
+          <t>32454; 48824</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37808; 53700</t>
+          <t>37540; 53930</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>36299; 50792</t>
+          <t>35571; 49868</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>100130; 126994</t>
+          <t>99017; 127190</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>84727; 110342</t>
+          <t>83198; 109559</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>106023; 131326</t>
+          <t>106125; 132157</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>89718; 113552</t>
+          <t>88547; 112814</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>41487; 64343</t>
+          <t>42196; 64674</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35494; 54681</t>
+          <t>35162; 55296</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>41290; 60522</t>
+          <t>40503; 60001</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58281; 79179</t>
+          <t>58640; 78477</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>18411; 29744</t>
+          <t>17969; 29179</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>12110; 24767</t>
+          <t>11769; 24855</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28378; 43060</t>
+          <t>28009; 43042</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>101178; 134541</t>
+          <t>100954; 135238</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64701; 90805</t>
+          <t>64280; 90571</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>52544; 75850</t>
+          <t>50912; 75776</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73803; 99653</t>
+          <t>73321; 98999</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>163284; 208868</t>
+          <t>165117; 211834</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21432; 34466</t>
+          <t>21546; 34482</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16804; 29246</t>
+          <t>17105; 29956</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20926; 34761</t>
+          <t>20240; 34313</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>34020; 49414</t>
+          <t>33919; 48989</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>988; 7680</t>
+          <t>977; 7601</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>10669; 20581</t>
+          <t>11077; 20796</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21076; 29712</t>
+          <t>20573; 29697</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33522; 43573</t>
+          <t>33634; 43361</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24070; 40045</t>
+          <t>24867; 40302</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32594; 48320</t>
+          <t>32260; 47582</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>45099; 62172</t>
+          <t>46532; 62262</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>71763; 89776</t>
+          <t>70796; 88869</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>0; 1070</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>157; 2923</t>
+          <t>158; 2923</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>659; 2914</t>
+          <t>941; 2914</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3158,12 +3158,12 @@
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>0; 1070</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1445; 5148</t>
+          <t>1489; 5190</t>
         </is>
       </c>
     </row>
@@ -3316,7 +3316,7 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>188; 821</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>188; 821</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>223693; 268198</t>
+          <t>222390; 267606</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>160143; 197915</t>
+          <t>159921; 196372</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>189336; 227259</t>
+          <t>189315; 228223</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>188867; 227692</t>
+          <t>188962; 227403</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>100160; 129872</t>
+          <t>98975; 128347</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>94801; 124703</t>
+          <t>96046; 125458</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>131567; 159313</t>
+          <t>131790; 158949</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>210530; 266559</t>
+          <t>211471; 267993</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>333659; 386773</t>
+          <t>334291; 387206</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>264194; 312849</t>
+          <t>265561; 316514</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>330461; 377016</t>
+          <t>331123; 377794</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>409751; 480048</t>
+          <t>410195; 477653</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/P6904-Edad-trans_dic.xlsx
+++ b/data/trans_dic/P6904-Edad-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>55,28%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>40,66%</t>
+          <t>41,84%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>46,77%</t>
         </is>
       </c>
     </row>
@@ -717,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>32,99; 61,54</t>
+          <t>33,71; 62,01</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11,07; 74,99</t>
+          <t>12,21; 79,72</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>24,13; 73,43</t>
+          <t>23,64; 74,02</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -737,42 +737,42 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>39,81; 82,18</t>
+          <t>39,14; 81,39</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>9,71; 69,71</t>
+          <t>9,51; 69,47</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>40,42; 91,62</t>
+          <t>40,7; 91,41</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,98; 75,72</t>
+          <t>13,07; 76,68</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>39,8; 65,04</t>
+          <t>39,54; 64,48</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>20,99; 64,73</t>
+          <t>19,75; 62,12</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>37,56; 73,51</t>
+          <t>36,31; 72,5</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,6; 66,63</t>
+          <t>21,47; 75,28</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>62,42%</t>
+          <t>63,48%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>51,85%</t>
+          <t>53,8%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>57,58%</t>
+          <t>59,36%</t>
         </is>
       </c>
     </row>
@@ -857,62 +857,62 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>39,32; 56,53</t>
+          <t>39,9; 56,52</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>43,44; 65,78</t>
+          <t>44,98; 66,74</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>47,73; 70,25</t>
+          <t>47,24; 69,73</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>44,89; 77,14</t>
+          <t>48,09; 77,91</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>31,0; 53,67</t>
+          <t>31,68; 53,95</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>34,98; 60,8</t>
+          <t>34,23; 59,41</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>48,32; 75,64</t>
+          <t>49,9; 75,5</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>37,51; 66,75</t>
+          <t>39,62; 68,05</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38,6; 52,89</t>
+          <t>38,48; 52,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>43,35; 60,62</t>
+          <t>44,86; 61,24</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>51,79; 68,86</t>
+          <t>51,48; 69,53</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>46,68; 68,94</t>
+          <t>48,39; 69,4</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>60,63%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>55,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>59,24%</t>
+          <t>59,37%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>49,11; 66,43</t>
+          <t>49,52; 67,04</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>47,64; 68,15</t>
+          <t>47,78; 68,89</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>54,39; 74,06</t>
+          <t>55,04; 72,85</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>50,38; 71,75</t>
+          <t>52,78; 72,01</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>45,19; 69,2</t>
+          <t>45,28; 68,78</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>44,68; 67,22</t>
+          <t>43,52; 68,23</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>52,53; 75,47</t>
+          <t>52,76; 75,0</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>47,08; 66,01</t>
+          <t>47,45; 65,11</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>50,5; 64,87</t>
+          <t>50,77; 65,3</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>49,06; 64,6</t>
+          <t>49,3; 64,6</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>57,5; 71,6</t>
+          <t>57,3; 71,48</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>51,76; 65,94</t>
+          <t>51,85; 65,73</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>63,12%</t>
+          <t>64,83%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>74,27%</t>
+          <t>66,0%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>69,67%</t>
+          <t>65,43%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>37,98; 58,21</t>
+          <t>38,89; 58,07</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>39,05; 61,4</t>
+          <t>40,25; 61,26</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>44,3; 65,63</t>
+          <t>44,35; 66,49</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>54,02; 72,29</t>
+          <t>55,32; 73,16</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>48,52; 78,78</t>
+          <t>47,66; 79,79</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,19; 61,64</t>
+          <t>29,52; 61,84</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>49,92; 76,71</t>
+          <t>49,54; 77,14</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>65,15; 87,28</t>
+          <t>59,25; 72,64</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>43,39; 61,14</t>
+          <t>43,25; 60,47</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>39,05; 58,12</t>
+          <t>39,51; 58,26</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>49,7; 67,1</t>
+          <t>50,09; 66,84</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>62,66; 80,39</t>
+          <t>59,76; 70,8</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>62,57%</t>
+          <t>63,31%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>69,35%</t>
+          <t>68,33%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>46,96; 75,15</t>
+          <t>48,02; 74,15</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>40,89; 71,61</t>
+          <t>42,59; 71,93</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>45,13; 76,51</t>
+          <t>47,69; 78,22</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>50,3; 72,65</t>
+          <t>51,54; 74,16</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,02; 54,65</t>
+          <t>7,04; 56,18</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,06; 84,6</t>
+          <t>45,16; 83,85</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>66,8; 96,42</t>
+          <t>66,64; 96,3</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>60,59; 78,12</t>
+          <t>59,25; 77,23</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>41,59; 67,4</t>
+          <t>41,89; 68,43</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>48,57; 71,64</t>
+          <t>48,38; 72,72</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>61,51; 82,31</t>
+          <t>58,75; 81,84</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>57,58; 72,28</t>
+          <t>58,19; 72,91</t>
         </is>
       </c>
     </row>
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>50,12%</t>
+          <t>56,47%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>72,91%</t>
+          <t>72,07%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>63,49%</t>
         </is>
       </c>
     </row>
@@ -1432,7 +1432,7 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>5,4; 100,0</t>
+          <t>13,96; 100,0</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>32,28; 100,0</t>
+          <t>22,35; 100,0</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
@@ -1472,7 +1472,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>25,51; 88,94</t>
+          <t>28,39; 87,8</t>
         </is>
       </c>
     </row>
@@ -1644,7 +1644,7 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>61,49%</t>
+          <t>63,26%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>65,29%</t>
+          <t>60,95%</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
@@ -1684,7 +1684,7 @@
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>63,43%</t>
+          <t>62,17%</t>
         </is>
       </c>
     </row>
@@ -1697,62 +1697,62 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>47,09; 56,66</t>
+          <t>47,51; 57,21</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>49,14; 60,34</t>
+          <t>48,93; 61,16</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>54,09; 65,21</t>
+          <t>54,02; 65,28</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>55,66; 66,98</t>
+          <t>57,69; 68,31</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>44,96; 58,31</t>
+          <t>44,66; 58,32</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>44,95; 58,72</t>
+          <t>44,7; 58,16</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>60,93; 73,49</t>
+          <t>60,78; 73,25</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>59,7; 75,66</t>
+          <t>56,39; 65,61</t>
         </is>
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>48,28; 55,92</t>
+          <t>48,48; 56,12</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>49,26; 58,71</t>
+          <t>49,01; 58,39</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>58,47; 66,71</t>
+          <t>58,22; 66,58</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>59,13; 68,85</t>
+          <t>58,06; 65,58</t>
         </is>
       </c>
     </row>
@@ -2015,7 +2015,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>1805</t>
+          <t>5096</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2035,7 +2035,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>6239</t>
+          <t>6652</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -2055,7 +2055,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8044</t>
+          <t>11748</t>
         </is>
       </c>
     </row>
@@ -2068,62 +2068,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>15234; 28416</t>
+          <t>15563; 28630</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>1143; 7744</t>
+          <t>1261; 8233</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>4138; 12594</t>
+          <t>4054; 12694</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 5989</t>
+          <t>0; 9218</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>7906; 16321</t>
+          <t>7772; 16163</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>977; 7010</t>
+          <t>957; 6986</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4706; 10667</t>
+          <t>4739; 10643</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>1685; 11618</t>
+          <t>2078; 12192</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>26279; 42944</t>
+          <t>26108; 42575</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>4279; 13194</t>
+          <t>4026; 12662</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10815; 21167</t>
+          <t>10454; 20875</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>2902; 14214</t>
+          <t>5392; 18907</t>
         </is>
       </c>
     </row>
@@ -2223,7 +2223,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36874</t>
+          <t>44181</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2243,7 +2243,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>25897</t>
+          <t>27713</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2263,7 +2263,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62771</t>
+          <t>71893</t>
         </is>
       </c>
     </row>
@@ -2276,62 +2276,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>55948; 80432</t>
+          <t>56777; 80422</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>37485; 56764</t>
+          <t>38812; 57592</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>38938; 57308</t>
+          <t>38533; 56882</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>26516; 45569</t>
+          <t>33466; 54222</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>24573; 42544</t>
+          <t>25113; 42765</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>23114; 40169</t>
+          <t>22616; 39251</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>22368; 35013</t>
+          <t>23097; 34951</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>18734; 33339</t>
+          <t>20409; 35052</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>85533; 117195</t>
+          <t>85268; 116543</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>66041; 92362</t>
+          <t>68350; 93310</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>66223; 88041</t>
+          <t>65825; 88907</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>50896; 75158</t>
+          <t>58607; 84049</t>
         </is>
       </c>
     </row>
@@ -2431,7 +2431,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>57919</t>
+          <t>68473</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2451,7 +2451,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>43432</t>
+          <t>48257</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>101351</t>
+          <t>116730</t>
         </is>
       </c>
     </row>
@@ -2484,62 +2484,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>61898; 83718</t>
+          <t>62411; 84492</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>46186; 66072</t>
+          <t>46330; 66797</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>61528; 83777</t>
+          <t>62263; 82405</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>48129; 68542</t>
+          <t>58045; 79193</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>31649; 48467</t>
+          <t>31715; 48178</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>32454; 48824</t>
+          <t>31607; 49555</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>37540; 53930</t>
+          <t>37703; 53590</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>35571; 49868</t>
+          <t>41109; 56414</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>99017; 127190</t>
+          <t>99549; 128039</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>83198; 109559</t>
+          <t>83599; 109551</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>106125; 132157</t>
+          <t>105768; 131932</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>88547; 112814</t>
+          <t>101950; 129240</t>
         </is>
       </c>
     </row>
@@ -2639,7 +2639,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>68515</t>
+          <t>78137</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2659,7 +2659,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>115075</t>
+          <t>83501</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>183590</t>
+          <t>161638</t>
         </is>
       </c>
     </row>
@@ -2692,62 +2692,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>42196; 64674</t>
+          <t>43212; 64521</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>35162; 55296</t>
+          <t>36244; 55167</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>40503; 60001</t>
+          <t>40549; 60787</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>58640; 78477</t>
+          <t>66671; 88177</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>17969; 29179</t>
+          <t>17652; 29552</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>11769; 24855</t>
+          <t>11902; 24933</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>28009; 43042</t>
+          <t>27793; 43283</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>100954; 135238</t>
+          <t>74961; 91904</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>64280; 90571</t>
+          <t>64075; 89588</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>50912; 75776</t>
+          <t>51516; 75958</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>73321; 98999</t>
+          <t>73894; 98610</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>165117; 211834</t>
+          <t>147635; 174903</t>
         </is>
       </c>
     </row>
@@ -2847,7 +2847,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>42196</t>
+          <t>45598</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2867,7 +2867,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>38492</t>
+          <t>42207</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2887,7 +2887,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>80688</t>
+          <t>87805</t>
         </is>
       </c>
     </row>
@@ -2900,62 +2900,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>21546; 34482</t>
+          <t>22034; 34021</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>17105; 29956</t>
+          <t>17819; 30090</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>20240; 34313</t>
+          <t>21389; 35081</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>33919; 48989</t>
+          <t>37121; 53410</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>977; 7601</t>
+          <t>980; 7814</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>11077; 20796</t>
+          <t>11101; 20613</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>20573; 29697</t>
+          <t>20524; 29659</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>33634; 43361</t>
+          <t>36599; 47704</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>24867; 40302</t>
+          <t>25045; 40916</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>32260; 47582</t>
+          <t>32133; 48295</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>46532; 62262</t>
+          <t>44442; 61910</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>70796; 88869</t>
+          <t>77858; 97549</t>
         </is>
       </c>
     </row>
@@ -3055,7 +3055,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>1465</t>
+          <t>2071</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -3075,7 +3075,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>2125</t>
+          <t>2161</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3589</t>
+          <t>4233</t>
         </is>
       </c>
     </row>
@@ -3123,7 +3123,7 @@
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>158; 2923</t>
+          <t>512; 3668</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -3143,7 +3143,7 @@
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>941; 2914</t>
+          <t>670; 2999</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>1489; 5190</t>
+          <t>1892; 5854</t>
         </is>
       </c>
     </row>
@@ -3471,7 +3471,7 @@
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>208774</t>
+          <t>243557</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3491,7 +3491,7 @@
       </c>
       <c r="J26" s="2" t="inlineStr">
         <is>
-          <t>231260</t>
+          <t>210491</t>
         </is>
       </c>
       <c r="K26" s="2" t="inlineStr">
@@ -3511,7 +3511,7 @@
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>440034</t>
+          <t>454048</t>
         </is>
       </c>
     </row>
@@ -3524,62 +3524,62 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>222390; 267606</t>
+          <t>224382; 270196</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>159921; 196372</t>
+          <t>159251; 199040</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>189315; 228223</t>
+          <t>189080; 228492</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>188962; 227403</t>
+          <t>222094; 262984</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>98975; 128347</t>
+          <t>98303; 128383</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>96046; 125458</t>
+          <t>95508; 124256</t>
         </is>
       </c>
       <c r="I27" s="2" t="inlineStr">
         <is>
-          <t>131790; 158949</t>
+          <t>131465; 158442</t>
         </is>
       </c>
       <c r="J27" s="2" t="inlineStr">
         <is>
-          <t>211471; 267993</t>
+          <t>194730; 226579</t>
         </is>
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>334291; 387206</t>
+          <t>335689; 388595</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>265561; 316514</t>
+          <t>264213; 314778</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>331123; 377794</t>
+          <t>329707; 377060</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
         <is>
-          <t>410195; 477653</t>
+          <t>424005; 478967</t>
         </is>
       </c>
     </row>
